--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -600,7 +600,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -8420,7 +8420,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -10122,7 +10122,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10674,7 +10674,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12146,7 +12146,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12422,7 +12422,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12698,7 +12698,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13848,7 +13848,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14538,7 +14538,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14814,7 +14814,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
@@ -2113,7 +2113,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:43</t>
+    <t xml:space="preserve">2026-09-07 12:50</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
@@ -2113,7 +2113,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:50</t>
+    <t xml:space="preserve">2026-09-08 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
